--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -1043,7 +1043,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121791510</v>
+        <v>121795558</v>
       </c>
       <c r="B5" t="n">
         <v>98113</v>
@@ -1078,27 +1078,30 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661731</v>
+        <v>661739</v>
       </c>
       <c r="R5" t="n">
-        <v>6685770</v>
+        <v>6685755</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,9 +1128,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,22 +1155,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121795518</v>
+        <v>121791510</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,53 +1179,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661615</v>
+        <v>661731</v>
       </c>
       <c r="R6" t="n">
-        <v>6685669</v>
+        <v>6685770</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,19 +1249,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,22 +1266,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121795558</v>
+        <v>121795530</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,50 +1290,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Storbya hjortronmosse, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661739</v>
+        <v>661649</v>
       </c>
       <c r="R7" t="n">
-        <v>6685755</v>
+        <v>6685585</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,10 +1402,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121795532</v>
+        <v>121795522</v>
       </c>
       <c r="B8" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1418,33 +1418,33 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1454,13 +1454,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661892</v>
+        <v>661736</v>
       </c>
       <c r="R8" t="n">
-        <v>6685589</v>
+        <v>6685773</v>
       </c>
       <c r="S8" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121795530</v>
+        <v>121791202</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>95660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,49 +1542,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storbya hjortronmosse, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661649</v>
+        <v>661692</v>
       </c>
       <c r="R9" t="n">
-        <v>6685585</v>
+        <v>6685628</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1611,19 +1599,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,19 +1616,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121795522</v>
+        <v>121795520</v>
       </c>
       <c r="B10" t="n">
         <v>57373</v>
@@ -1692,20 +1670,20 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661736</v>
+        <v>661629</v>
       </c>
       <c r="R10" t="n">
-        <v>6685773</v>
+        <v>6685692</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1737,7 +1715,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1747,7 +1725,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121795526</v>
+        <v>121795532</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1790,33 +1768,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1826,13 +1804,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661776</v>
+        <v>661892</v>
       </c>
       <c r="R11" t="n">
-        <v>6685559</v>
+        <v>6685589</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1861,7 +1839,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1871,7 +1849,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,10 +1876,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121795524</v>
+        <v>121791487</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1910,53 +1888,50 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661817</v>
+        <v>661747</v>
       </c>
       <c r="R12" t="n">
-        <v>6685662</v>
+        <v>6685756</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1983,19 +1958,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2010,22 +1975,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121791202</v>
+        <v>121795556</v>
       </c>
       <c r="B13" t="n">
-        <v>95660</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2034,41 +1999,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661692</v>
+        <v>661611</v>
       </c>
       <c r="R13" t="n">
-        <v>6685628</v>
+        <v>6685709</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2095,9 +2072,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,22 +2099,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121791487</v>
+        <v>121795524</v>
       </c>
       <c r="B14" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2136,50 +2123,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661747</v>
+        <v>661817</v>
       </c>
       <c r="R14" t="n">
-        <v>6685756</v>
+        <v>6685662</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2206,9 +2196,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2223,19 +2223,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121795520</v>
+        <v>121795518</v>
       </c>
       <c r="B15" t="n">
         <v>57373</v>
@@ -2277,7 +2277,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661629</v>
+        <v>661615</v>
       </c>
       <c r="R15" t="n">
-        <v>6685692</v>
+        <v>6685669</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2474,10 +2474,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121795556</v>
+        <v>121795526</v>
       </c>
       <c r="B17" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2486,50 +2486,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661611</v>
+        <v>661776</v>
       </c>
       <c r="R17" t="n">
-        <v>6685709</v>
+        <v>6685559</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -1987,10 +1987,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121795556</v>
+        <v>121795524</v>
       </c>
       <c r="B13" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,50 +1999,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661611</v>
+        <v>661817</v>
       </c>
       <c r="R13" t="n">
-        <v>6685709</v>
+        <v>6685662</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2074,7 +2074,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2111,10 +2111,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121795524</v>
+        <v>121795556</v>
       </c>
       <c r="B14" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2123,50 +2123,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661817</v>
+        <v>661611</v>
       </c>
       <c r="R14" t="n">
-        <v>6685662</v>
+        <v>6685709</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121795558</v>
+        <v>121795524</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,39 +1055,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661739</v>
+        <v>661817</v>
       </c>
       <c r="R5" t="n">
-        <v>6685755</v>
+        <v>6685662</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121791510</v>
+        <v>121795520</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,50 +1179,53 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661731</v>
+        <v>661629</v>
       </c>
       <c r="R6" t="n">
-        <v>6685770</v>
+        <v>6685692</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,9 +1252,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,12 +1279,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1402,7 +1415,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121795522</v>
+        <v>121795518</v>
       </c>
       <c r="B8" t="n">
         <v>57373</v>
@@ -1450,14 +1463,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661736</v>
+        <v>661615</v>
       </c>
       <c r="R8" t="n">
-        <v>6685773</v>
+        <v>6685669</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1489,7 +1502,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1499,7 +1512,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121791202</v>
+        <v>121791487</v>
       </c>
       <c r="B9" t="n">
-        <v>95660</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,38 +1551,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661692</v>
+        <v>661747</v>
       </c>
       <c r="R9" t="n">
-        <v>6685628</v>
+        <v>6685756</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1628,7 +1650,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121795520</v>
+        <v>121795526</v>
       </c>
       <c r="B10" t="n">
         <v>57373</v>
@@ -1670,20 +1692,20 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661629</v>
+        <v>661776</v>
       </c>
       <c r="R10" t="n">
-        <v>6685692</v>
+        <v>6685559</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1715,7 +1737,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1725,7 +1747,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,10 +1774,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121795532</v>
+        <v>121795522</v>
       </c>
       <c r="B11" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,33 +1790,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1804,13 +1826,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661892</v>
+        <v>661736</v>
       </c>
       <c r="R11" t="n">
-        <v>6685589</v>
+        <v>6685773</v>
       </c>
       <c r="S11" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1839,7 +1861,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1849,7 +1871,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1876,10 +1898,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121791487</v>
+        <v>121795532</v>
       </c>
       <c r="B12" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1888,50 +1910,53 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661747</v>
+        <v>661892</v>
       </c>
       <c r="R12" t="n">
-        <v>6685756</v>
+        <v>6685589</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1958,9 +1983,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,22 +2010,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121795524</v>
+        <v>121791510</v>
       </c>
       <c r="B13" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,53 +2034,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661817</v>
+        <v>661731</v>
       </c>
       <c r="R13" t="n">
-        <v>6685662</v>
+        <v>6685770</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2072,19 +2104,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2099,19 +2121,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121795556</v>
+        <v>121795558</v>
       </c>
       <c r="B14" t="n">
         <v>98113</v>
@@ -2146,7 +2168,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2159,14 +2181,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661611</v>
+        <v>661739</v>
       </c>
       <c r="R14" t="n">
-        <v>6685709</v>
+        <v>6685755</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2198,7 +2220,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2208,7 +2230,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2235,10 +2257,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121795518</v>
+        <v>121791202</v>
       </c>
       <c r="B15" t="n">
-        <v>57373</v>
+        <v>95660</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,49 +2273,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661615</v>
+        <v>661692</v>
       </c>
       <c r="R15" t="n">
-        <v>6685669</v>
+        <v>6685628</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2320,19 +2330,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2347,12 +2347,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2474,10 +2474,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121795526</v>
+        <v>121795556</v>
       </c>
       <c r="B17" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2486,50 +2486,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661776</v>
+        <v>661611</v>
       </c>
       <c r="R17" t="n">
-        <v>6685559</v>
+        <v>6685709</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -1415,10 +1415,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121795518</v>
+        <v>121791487</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,53 +1427,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661615</v>
+        <v>661747</v>
       </c>
       <c r="R8" t="n">
-        <v>6685669</v>
+        <v>6685756</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1500,19 +1497,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,22 +1514,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121791487</v>
+        <v>121795518</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1551,50 +1538,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661747</v>
+        <v>661615</v>
       </c>
       <c r="R9" t="n">
-        <v>6685756</v>
+        <v>6685669</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1621,9 +1611,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,12 +1638,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121795524</v>
+        <v>121791510</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,53 +1055,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661817</v>
+        <v>661731</v>
       </c>
       <c r="R5" t="n">
-        <v>6685662</v>
+        <v>6685770</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,19 +1125,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:51</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,12 +1142,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1291,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121795530</v>
+        <v>121791487</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1303,53 +1290,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storbya hjortronmosse, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661649</v>
+        <v>661747</v>
       </c>
       <c r="R7" t="n">
-        <v>6685585</v>
+        <v>6685756</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,19 +1360,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1403,22 +1377,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121791487</v>
+        <v>121795526</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,50 +1401,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661747</v>
+        <v>661776</v>
       </c>
       <c r="R8" t="n">
-        <v>6685756</v>
+        <v>6685559</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1497,9 +1474,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,22 +1501,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121795518</v>
+        <v>121791202</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>95660</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,49 +1529,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661615</v>
+        <v>661692</v>
       </c>
       <c r="R9" t="n">
-        <v>6685669</v>
+        <v>6685628</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1611,19 +1586,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1638,22 +1603,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121795526</v>
+        <v>121795537</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1666,35 +1631,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1702,10 +1658,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661776</v>
+        <v>661964</v>
       </c>
       <c r="R10" t="n">
-        <v>6685559</v>
+        <v>6685515</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1737,7 +1693,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1747,7 +1703,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121795522</v>
+        <v>121795558</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1786,39 +1742,39 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1826,10 +1782,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661736</v>
+        <v>661739</v>
       </c>
       <c r="R11" t="n">
-        <v>6685773</v>
+        <v>6685755</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1861,7 +1817,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1871,7 +1827,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1898,10 +1854,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121795532</v>
+        <v>121795524</v>
       </c>
       <c r="B12" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1914,33 +1870,33 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1950,13 +1906,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661892</v>
+        <v>661817</v>
       </c>
       <c r="R12" t="n">
-        <v>6685589</v>
+        <v>6685662</v>
       </c>
       <c r="S12" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1985,7 +1941,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1995,7 +1951,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2022,10 +1978,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121791510</v>
+        <v>121795532</v>
       </c>
       <c r="B13" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2034,50 +1990,53 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661731</v>
+        <v>661892</v>
       </c>
       <c r="R13" t="n">
-        <v>6685770</v>
+        <v>6685589</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2104,9 +2063,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2121,19 +2090,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121795558</v>
+        <v>121795556</v>
       </c>
       <c r="B14" t="n">
         <v>98113</v>
@@ -2168,7 +2137,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2181,14 +2150,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661739</v>
+        <v>661611</v>
       </c>
       <c r="R14" t="n">
-        <v>6685755</v>
+        <v>6685709</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2220,7 +2189,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2230,7 +2199,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2257,10 +2226,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121791202</v>
+        <v>121795530</v>
       </c>
       <c r="B15" t="n">
-        <v>95660</v>
+        <v>57373</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2273,37 +2242,49 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Storbya hjortronmosse, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661692</v>
+        <v>661649</v>
       </c>
       <c r="R15" t="n">
-        <v>6685628</v>
+        <v>6685585</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2330,9 +2311,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2347,22 +2338,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121795537</v>
+        <v>121795522</v>
       </c>
       <c r="B16" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2375,26 +2366,35 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661964</v>
+        <v>661736</v>
       </c>
       <c r="R16" t="n">
-        <v>6685515</v>
+        <v>6685773</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2474,10 +2474,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121795556</v>
+        <v>121795518</v>
       </c>
       <c r="B17" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2486,39 +2486,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661611</v>
+        <v>661615</v>
       </c>
       <c r="R17" t="n">
-        <v>6685709</v>
+        <v>6685669</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121791510</v>
+        <v>121795520</v>
       </c>
       <c r="B5" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,50 +1055,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661731</v>
+        <v>661629</v>
       </c>
       <c r="R5" t="n">
-        <v>6685770</v>
+        <v>6685692</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1125,9 +1128,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,22 +1155,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121795520</v>
+        <v>121795558</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1166,50 +1179,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661629</v>
+        <v>661739</v>
       </c>
       <c r="R6" t="n">
-        <v>6685692</v>
+        <v>6685755</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1241,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,7 +1264,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1291,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121791487</v>
+        <v>121795537</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,50 +1303,44 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661747</v>
+        <v>661964</v>
       </c>
       <c r="R7" t="n">
-        <v>6685756</v>
+        <v>6685515</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1360,9 +1367,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,19 +1394,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121795526</v>
+        <v>121795522</v>
       </c>
       <c r="B8" t="n">
         <v>57373</v>
@@ -1441,10 +1458,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661776</v>
+        <v>661736</v>
       </c>
       <c r="R8" t="n">
-        <v>6685559</v>
+        <v>6685773</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1476,7 +1493,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1486,7 +1503,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,10 +1530,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121791202</v>
+        <v>121791487</v>
       </c>
       <c r="B9" t="n">
-        <v>95660</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1525,38 +1542,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661692</v>
+        <v>661747</v>
       </c>
       <c r="R9" t="n">
-        <v>6685628</v>
+        <v>6685756</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1615,10 +1641,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121795537</v>
+        <v>121795524</v>
       </c>
       <c r="B10" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,26 +1657,35 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1658,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661964</v>
+        <v>661817</v>
       </c>
       <c r="R10" t="n">
-        <v>6685515</v>
+        <v>6685662</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1693,7 +1728,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1703,7 +1738,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,10 +1765,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121795558</v>
+        <v>121791202</v>
       </c>
       <c r="B11" t="n">
-        <v>98113</v>
+        <v>95660</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,53 +1777,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661739</v>
+        <v>661692</v>
       </c>
       <c r="R11" t="n">
-        <v>6685755</v>
+        <v>6685628</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1815,19 +1838,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,19 +1855,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121795524</v>
+        <v>121795518</v>
       </c>
       <c r="B12" t="n">
         <v>57373</v>
@@ -1896,20 +1909,20 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661817</v>
+        <v>661615</v>
       </c>
       <c r="R12" t="n">
-        <v>6685662</v>
+        <v>6685669</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1941,7 +1954,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1951,7 +1964,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2102,10 +2115,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121795556</v>
+        <v>121795530</v>
       </c>
       <c r="B14" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2114,50 +2127,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Storbya hjortronmosse, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661611</v>
+        <v>661649</v>
       </c>
       <c r="R14" t="n">
-        <v>6685709</v>
+        <v>6685585</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2189,7 +2202,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2199,7 +2212,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2226,7 +2239,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121795530</v>
+        <v>121795526</v>
       </c>
       <c r="B15" t="n">
         <v>57373</v>
@@ -2268,20 +2281,20 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storbya hjortronmosse, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661649</v>
+        <v>661776</v>
       </c>
       <c r="R15" t="n">
-        <v>6685585</v>
+        <v>6685559</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2313,7 +2326,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2323,7 +2336,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2350,10 +2363,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121795522</v>
+        <v>121795556</v>
       </c>
       <c r="B16" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2362,50 +2375,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661736</v>
+        <v>661611</v>
       </c>
       <c r="R16" t="n">
-        <v>6685773</v>
+        <v>6685709</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2437,7 +2450,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2447,7 +2460,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2474,10 +2487,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121795518</v>
+        <v>121791510</v>
       </c>
       <c r="B17" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2486,53 +2499,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661615</v>
+        <v>661731</v>
       </c>
       <c r="R17" t="n">
-        <v>6685669</v>
+        <v>6685770</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2559,19 +2569,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,12 +2586,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -1043,7 +1043,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121795520</v>
+        <v>121795518</v>
       </c>
       <c r="B5" t="n">
         <v>57373</v>
@@ -1085,7 +1085,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661629</v>
+        <v>661615</v>
       </c>
       <c r="R5" t="n">
-        <v>6685692</v>
+        <v>6685669</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,10 +1167,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121795558</v>
+        <v>121795524</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,39 +1179,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661739</v>
+        <v>661817</v>
       </c>
       <c r="R6" t="n">
-        <v>6685755</v>
+        <v>6685662</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,10 +1291,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121795537</v>
+        <v>121791202</v>
       </c>
       <c r="B7" t="n">
-        <v>90728</v>
+        <v>95660</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,40 +1307,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661964</v>
+        <v>661692</v>
       </c>
       <c r="R7" t="n">
-        <v>6685515</v>
+        <v>6685628</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1367,19 +1364,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,19 +1381,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121795522</v>
+        <v>121795530</v>
       </c>
       <c r="B8" t="n">
         <v>57373</v>
@@ -1448,20 +1435,20 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Storbya hjortronmosse, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661736</v>
+        <v>661649</v>
       </c>
       <c r="R8" t="n">
-        <v>6685773</v>
+        <v>6685585</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1493,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1503,7 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,7 +1517,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121791487</v>
+        <v>121791510</v>
       </c>
       <c r="B9" t="n">
         <v>98113</v>
@@ -1565,7 +1552,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1579,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661747</v>
+        <v>661731</v>
       </c>
       <c r="R9" t="n">
-        <v>6685756</v>
+        <v>6685770</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1641,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121795524</v>
+        <v>121795558</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,39 +1640,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1693,10 +1680,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661817</v>
+        <v>661739</v>
       </c>
       <c r="R10" t="n">
-        <v>6685662</v>
+        <v>6685755</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1728,7 +1715,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1738,7 +1725,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121791202</v>
+        <v>121795537</v>
       </c>
       <c r="B11" t="n">
-        <v>95660</v>
+        <v>90728</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1781,37 +1768,40 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661692</v>
+        <v>661964</v>
       </c>
       <c r="R11" t="n">
-        <v>6685628</v>
+        <v>6685515</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1838,9 +1828,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,19 +1855,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121795518</v>
+        <v>121795526</v>
       </c>
       <c r="B12" t="n">
         <v>57373</v>
@@ -1915,14 +1915,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661615</v>
+        <v>661776</v>
       </c>
       <c r="R12" t="n">
-        <v>6685669</v>
+        <v>6685559</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,10 +1991,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121795532</v>
+        <v>121795522</v>
       </c>
       <c r="B13" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,33 +2007,33 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2043,13 +2043,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661892</v>
+        <v>661736</v>
       </c>
       <c r="R13" t="n">
-        <v>6685589</v>
+        <v>6685773</v>
       </c>
       <c r="S13" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2115,10 +2115,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121795530</v>
+        <v>121795532</v>
       </c>
       <c r="B14" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2131,49 +2131,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storbya hjortronmosse, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661649</v>
+        <v>661892</v>
       </c>
       <c r="R14" t="n">
-        <v>6685585</v>
+        <v>6685589</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2239,10 +2239,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121795526</v>
+        <v>121795556</v>
       </c>
       <c r="B15" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2251,50 +2251,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661776</v>
+        <v>661611</v>
       </c>
       <c r="R15" t="n">
-        <v>6685559</v>
+        <v>6685709</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2363,7 +2363,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121795556</v>
+        <v>121791487</v>
       </c>
       <c r="B16" t="n">
         <v>98113</v>
@@ -2398,30 +2398,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661611</v>
+        <v>661747</v>
       </c>
       <c r="R16" t="n">
-        <v>6685709</v>
+        <v>6685756</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2448,19 +2445,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2475,22 +2462,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121791510</v>
+        <v>121795520</v>
       </c>
       <c r="B17" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2499,50 +2486,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661731</v>
+        <v>661629</v>
       </c>
       <c r="R17" t="n">
-        <v>6685770</v>
+        <v>6685692</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2569,9 +2559,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,12 +2586,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121795518</v>
+        <v>121791202</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>95660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,49 +1059,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661615</v>
+        <v>661692</v>
       </c>
       <c r="R5" t="n">
-        <v>6685669</v>
+        <v>6685628</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,19 +1116,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,22 +1133,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121795524</v>
+        <v>121795556</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1179,50 +1157,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661817</v>
+        <v>661611</v>
       </c>
       <c r="R6" t="n">
-        <v>6685662</v>
+        <v>6685709</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1254,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1264,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121791202</v>
+        <v>121795524</v>
       </c>
       <c r="B7" t="n">
-        <v>95660</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,37 +1285,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661692</v>
+        <v>661817</v>
       </c>
       <c r="R7" t="n">
-        <v>6685628</v>
+        <v>6685662</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,9 +1354,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,22 +1381,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121795530</v>
+        <v>121795558</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,50 +1405,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storbya hjortronmosse, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661649</v>
+        <v>661739</v>
       </c>
       <c r="R8" t="n">
-        <v>6685585</v>
+        <v>6685755</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121791510</v>
+        <v>121795532</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>57510</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,50 +1529,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661731</v>
+        <v>661892</v>
       </c>
       <c r="R9" t="n">
-        <v>6685770</v>
+        <v>6685589</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1599,9 +1602,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,22 +1629,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121795558</v>
+        <v>121795522</v>
       </c>
       <c r="B10" t="n">
-        <v>98113</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,39 +1653,39 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1680,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661739</v>
+        <v>661736</v>
       </c>
       <c r="R10" t="n">
-        <v>6685755</v>
+        <v>6685773</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1715,7 +1728,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1725,7 +1738,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,10 +1765,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121795537</v>
+        <v>121795518</v>
       </c>
       <c r="B11" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,37 +1781,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661964</v>
+        <v>661615</v>
       </c>
       <c r="R11" t="n">
-        <v>6685515</v>
+        <v>6685669</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1830,7 +1852,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1840,7 +1862,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1867,7 +1889,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121795526</v>
+        <v>121795520</v>
       </c>
       <c r="B12" t="n">
         <v>57373</v>
@@ -1909,20 +1931,20 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661776</v>
+        <v>661629</v>
       </c>
       <c r="R12" t="n">
-        <v>6685559</v>
+        <v>6685692</v>
       </c>
       <c r="S12" t="n">
         <v>4</v>
@@ -1954,7 +1976,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1964,7 +1986,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1991,10 +2013,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121795522</v>
+        <v>121791487</v>
       </c>
       <c r="B13" t="n">
-        <v>57373</v>
+        <v>98113</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2003,53 +2025,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661736</v>
+        <v>661747</v>
       </c>
       <c r="R13" t="n">
-        <v>6685773</v>
+        <v>6685756</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2076,19 +2095,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2103,22 +2112,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121795532</v>
+        <v>121795526</v>
       </c>
       <c r="B14" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2131,33 +2140,33 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2167,13 +2176,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661892</v>
+        <v>661776</v>
       </c>
       <c r="R14" t="n">
-        <v>6685589</v>
+        <v>6685559</v>
       </c>
       <c r="S14" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2202,7 +2211,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2212,7 +2221,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2239,7 +2248,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121795556</v>
+        <v>121791510</v>
       </c>
       <c r="B15" t="n">
         <v>98113</v>
@@ -2274,30 +2283,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661611</v>
+        <v>661731</v>
       </c>
       <c r="R15" t="n">
-        <v>6685709</v>
+        <v>6685770</v>
       </c>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2324,19 +2330,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2351,22 +2347,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121791487</v>
+        <v>121795537</v>
       </c>
       <c r="B16" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2375,50 +2371,44 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661747</v>
+        <v>661964</v>
       </c>
       <c r="R16" t="n">
-        <v>6685756</v>
+        <v>6685515</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2445,9 +2435,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2462,19 +2462,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121795520</v>
+        <v>121795530</v>
       </c>
       <c r="B17" t="n">
         <v>57373</v>
@@ -2522,14 +2522,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Storbya hjortronmosse, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661629</v>
+        <v>661649</v>
       </c>
       <c r="R17" t="n">
-        <v>6685692</v>
+        <v>6685585</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121795532</v>
+        <v>121795522</v>
       </c>
       <c r="B9" t="n">
-        <v>57510</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1533,33 +1533,33 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1569,13 +1569,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661892</v>
+        <v>661736</v>
       </c>
       <c r="R9" t="n">
-        <v>6685589</v>
+        <v>6685773</v>
       </c>
       <c r="S9" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1641,10 +1641,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121795522</v>
+        <v>121795532</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>57510</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1657,33 +1657,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1693,13 +1693,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661736</v>
+        <v>661892</v>
       </c>
       <c r="R10" t="n">
-        <v>6685773</v>
+        <v>6685589</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2359,10 +2359,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121795537</v>
+        <v>121795530</v>
       </c>
       <c r="B16" t="n">
-        <v>90728</v>
+        <v>57373</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2375,37 +2375,46 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Storbya hjortronmosse, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661964</v>
+        <v>661649</v>
       </c>
       <c r="R16" t="n">
-        <v>6685515</v>
+        <v>6685585</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2437,7 +2446,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2447,7 +2456,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2474,10 +2483,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121795530</v>
+        <v>121795537</v>
       </c>
       <c r="B17" t="n">
-        <v>57373</v>
+        <v>90728</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2490,46 +2499,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storbya hjortronmosse, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661649</v>
+        <v>661964</v>
       </c>
       <c r="R17" t="n">
-        <v>6685585</v>
+        <v>6685515</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121791202</v>
+        <v>121791510</v>
       </c>
       <c r="B5" t="n">
-        <v>95660</v>
+        <v>98131</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,38 +1055,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661692</v>
+        <v>661731</v>
       </c>
       <c r="R5" t="n">
-        <v>6685628</v>
+        <v>6685770</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1145,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121795556</v>
+        <v>121795524</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>57381</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,50 +1166,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661611</v>
+        <v>661817</v>
       </c>
       <c r="R6" t="n">
-        <v>6685709</v>
+        <v>6685662</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1232,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1251,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121795524</v>
+        <v>121795537</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>90742</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,35 +1294,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661817</v>
+        <v>661964</v>
       </c>
       <c r="R7" t="n">
-        <v>6685662</v>
+        <v>6685515</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,10 +1393,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121795558</v>
+        <v>121795520</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
+        <v>57381</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,50 +1405,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661739</v>
+        <v>661629</v>
       </c>
       <c r="R8" t="n">
-        <v>6685755</v>
+        <v>6685692</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,10 +1517,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121795522</v>
+        <v>121791487</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>98131</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,53 +1529,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661736</v>
+        <v>661747</v>
       </c>
       <c r="R9" t="n">
-        <v>6685773</v>
+        <v>6685756</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1602,19 +1599,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:35</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,22 +1616,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121795532</v>
+        <v>121795526</v>
       </c>
       <c r="B10" t="n">
-        <v>57510</v>
+        <v>57381</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1657,33 +1644,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1693,13 +1680,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661892</v>
+        <v>661776</v>
       </c>
       <c r="R10" t="n">
-        <v>6685589</v>
+        <v>6685559</v>
       </c>
       <c r="S10" t="n">
-        <v>88</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1728,7 +1715,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1738,7 +1725,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1765,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121795518</v>
+        <v>121795522</v>
       </c>
       <c r="B11" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1813,14 +1800,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661615</v>
+        <v>661736</v>
       </c>
       <c r="R11" t="n">
-        <v>6685669</v>
+        <v>6685773</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1852,7 +1839,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1862,7 +1849,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,10 +1876,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121795520</v>
+        <v>121795532</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>57518</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1905,49 +1892,49 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661629</v>
+        <v>661892</v>
       </c>
       <c r="R12" t="n">
-        <v>6685692</v>
+        <v>6685589</v>
       </c>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1976,7 +1963,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1986,7 +1973,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2013,10 +2000,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121791487</v>
+        <v>121795558</v>
       </c>
       <c r="B13" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2048,27 +2035,30 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661747</v>
+        <v>661739</v>
       </c>
       <c r="R13" t="n">
-        <v>6685756</v>
+        <v>6685755</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2095,9 +2085,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,22 +2112,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121795526</v>
+        <v>121795530</v>
       </c>
       <c r="B14" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2166,20 +2166,20 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Storbya hjortronmosse, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661776</v>
+        <v>661649</v>
       </c>
       <c r="R14" t="n">
-        <v>6685559</v>
+        <v>6685585</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,10 +2248,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121791510</v>
+        <v>121795556</v>
       </c>
       <c r="B15" t="n">
-        <v>98113</v>
+        <v>98131</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2283,27 +2283,30 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661731</v>
+        <v>661611</v>
       </c>
       <c r="R15" t="n">
-        <v>6685770</v>
+        <v>6685709</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2330,9 +2333,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2347,22 +2360,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121795530</v>
+        <v>121795518</v>
       </c>
       <c r="B16" t="n">
-        <v>57373</v>
+        <v>57381</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2401,20 +2414,20 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storbya hjortronmosse, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661649</v>
+        <v>661615</v>
       </c>
       <c r="R16" t="n">
-        <v>6685585</v>
+        <v>6685669</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2446,7 +2459,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2456,7 +2469,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2483,10 +2496,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121795537</v>
+        <v>121791202</v>
       </c>
       <c r="B17" t="n">
-        <v>90728</v>
+        <v>95678</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2499,40 +2512,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661964</v>
+        <v>661692</v>
       </c>
       <c r="R17" t="n">
-        <v>6685515</v>
+        <v>6685628</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2559,19 +2569,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,12 +2586,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121795524</v>
+        <v>121795537</v>
       </c>
       <c r="B6" t="n">
-        <v>57381</v>
+        <v>90742</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,35 +1170,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1206,10 +1197,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661817</v>
+        <v>661964</v>
       </c>
       <c r="R6" t="n">
-        <v>6685662</v>
+        <v>6685515</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1241,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1251,7 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121795537</v>
+        <v>121795524</v>
       </c>
       <c r="B7" t="n">
-        <v>90742</v>
+        <v>57381</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,26 +1285,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661964</v>
+        <v>661817</v>
       </c>
       <c r="R7" t="n">
-        <v>6685515</v>
+        <v>6685662</v>
       </c>
       <c r="S7" t="n">
         <v>4</v>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>121791510</v>
       </c>
       <c r="B5" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121795537</v>
+        <v>121795530</v>
       </c>
       <c r="B6" t="n">
-        <v>90742</v>
+        <v>57381</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,37 +1170,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Storbya hjortronmosse, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661964</v>
+        <v>661649</v>
       </c>
       <c r="R6" t="n">
-        <v>6685515</v>
+        <v>6685585</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1232,7 +1241,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1251,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1393,7 +1402,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121795520</v>
+        <v>121795522</v>
       </c>
       <c r="B8" t="n">
         <v>57381</v>
@@ -1435,20 +1444,20 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661629</v>
+        <v>661736</v>
       </c>
       <c r="R8" t="n">
-        <v>6685692</v>
+        <v>6685773</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1480,7 +1489,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,7 +1499,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1517,10 +1526,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121791487</v>
+        <v>121795518</v>
       </c>
       <c r="B9" t="n">
-        <v>98131</v>
+        <v>57381</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,50 +1538,53 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661747</v>
+        <v>661615</v>
       </c>
       <c r="R9" t="n">
-        <v>6685756</v>
+        <v>6685669</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1599,9 +1611,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,22 +1638,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121795526</v>
+        <v>121795537</v>
       </c>
       <c r="B10" t="n">
-        <v>57381</v>
+        <v>90744</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1644,35 +1666,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1680,10 +1693,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661776</v>
+        <v>661964</v>
       </c>
       <c r="R10" t="n">
-        <v>6685559</v>
+        <v>6685515</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1715,7 +1728,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1725,7 +1738,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1752,10 +1765,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121795522</v>
+        <v>121795556</v>
       </c>
       <c r="B11" t="n">
-        <v>57381</v>
+        <v>98133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1764,50 +1777,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661736</v>
+        <v>661611</v>
       </c>
       <c r="R11" t="n">
-        <v>6685773</v>
+        <v>6685709</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1839,7 +1852,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1849,7 +1862,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1876,10 +1889,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121795532</v>
+        <v>121791202</v>
       </c>
       <c r="B12" t="n">
-        <v>57518</v>
+        <v>95680</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1892,49 +1905,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661892</v>
+        <v>661692</v>
       </c>
       <c r="R12" t="n">
-        <v>6685589</v>
+        <v>6685628</v>
       </c>
       <c r="S12" t="n">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1961,19 +1962,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,22 +1979,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121795558</v>
+        <v>121791487</v>
       </c>
       <c r="B13" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2035,30 +2026,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661739</v>
+        <v>661747</v>
       </c>
       <c r="R13" t="n">
-        <v>6685755</v>
+        <v>6685756</v>
       </c>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2085,19 +2073,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>12:43</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2112,22 +2090,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121795530</v>
+        <v>121795532</v>
       </c>
       <c r="B14" t="n">
-        <v>57381</v>
+        <v>57518</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2140,49 +2118,49 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storbya hjortronmosse, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661649</v>
+        <v>661892</v>
       </c>
       <c r="R14" t="n">
-        <v>6685585</v>
+        <v>6685589</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2211,7 +2189,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2221,7 +2199,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,10 +2226,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121795556</v>
+        <v>121795558</v>
       </c>
       <c r="B15" t="n">
-        <v>98131</v>
+        <v>98133</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2283,7 +2261,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2296,14 +2274,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661611</v>
+        <v>661739</v>
       </c>
       <c r="R15" t="n">
-        <v>6685709</v>
+        <v>6685755</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2335,7 +2313,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,7 +2323,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,7 +2350,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121795518</v>
+        <v>121795520</v>
       </c>
       <c r="B16" t="n">
         <v>57381</v>
@@ -2414,7 +2392,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -2424,10 +2402,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661615</v>
+        <v>661629</v>
       </c>
       <c r="R16" t="n">
-        <v>6685669</v>
+        <v>6685692</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2459,7 +2437,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2469,7 +2447,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2496,10 +2474,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121791202</v>
+        <v>121795526</v>
       </c>
       <c r="B17" t="n">
-        <v>95678</v>
+        <v>57381</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2512,37 +2490,49 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661692</v>
+        <v>661776</v>
       </c>
       <c r="R17" t="n">
-        <v>6685628</v>
+        <v>6685559</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2569,9 +2559,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,12 +2586,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -2477,11 +2477,11 @@
         <v>121795532</v>
       </c>
       <c r="B17" t="n">
-        <v>57527</v>
+        <v>57631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -2477,7 +2477,7 @@
         <v>121795532</v>
       </c>
       <c r="B17" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4956367</v>
+        <v>121791202</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sjudars, 1,0 km V-ut, Upl</t>
+          <t>Andersön, Andersön, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661707.5369489306</v>
+        <v>661692</v>
       </c>
       <c r="R2" t="n">
-        <v>6685643.998580274</v>
+        <v>6685628</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-10-30</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-10-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,40 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1771771</v>
+        <v>121795546</v>
       </c>
       <c r="B3" t="n">
-        <v>88806</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,37 +783,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5685</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sjudars, 1,0 km V-ut, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661702.9103584668</v>
+        <v>661775</v>
       </c>
       <c r="R3" t="n">
-        <v>6685624.918050254</v>
+        <v>6685516</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +841,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-10-30</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-10-30</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,83 +867,67 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>tallåga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1161035</v>
+        <v>121795537</v>
       </c>
       <c r="B4" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sjudars, 1,0 km V-ut, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661783.6997837127</v>
+        <v>661964</v>
       </c>
       <c r="R4" t="n">
-        <v>6685575.849764216</v>
+        <v>6685515</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +951,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-10-30</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-10-30</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,67 +977,54 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121795537</v>
+        <v>121795539</v>
       </c>
       <c r="B5" t="n">
-        <v>90763</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1086,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661964</v>
+        <v>661766</v>
       </c>
       <c r="R5" t="n">
-        <v>6685515</v>
+        <v>6685520</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1121,7 +1067,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1131,7 +1077,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,65 +1104,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121795558</v>
+        <v>1161035</v>
       </c>
       <c r="B6" t="n">
-        <v>98159</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Sjudars, 1,0 km V-ut, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661739</v>
+        <v>661784</v>
       </c>
       <c r="R6" t="n">
-        <v>6685755</v>
+        <v>6685576</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,22 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:43</t>
+          <t>2011-10-30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:44</t>
+          <t>2011-10-30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,81 +1185,73 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121795522</v>
+        <v>1771771</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91282</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Sjudars, 1,0 km V-ut, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661736</v>
+        <v>661703</v>
       </c>
       <c r="R7" t="n">
-        <v>6685773</v>
+        <v>6685625</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1364,22 +1275,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2011-10-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:35</t>
+          <t>2011-10-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,67 +1291,76 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Annika Rastén</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121795556</v>
+        <v>121795518</v>
       </c>
       <c r="B8" t="n">
-        <v>98159</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1458,10 +1368,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661611</v>
+        <v>661615</v>
       </c>
       <c r="R8" t="n">
-        <v>6685709</v>
+        <v>6685669</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1493,7 +1403,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1503,7 +1413,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1530,19 +1440,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121795530</v>
+        <v>121795520</v>
       </c>
       <c r="B9" t="n">
-        <v>57390</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1578,14 +1483,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storbya hjortronmosse, Upl</t>
+          <t>Andersön, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>661649</v>
+        <v>661629</v>
       </c>
       <c r="R9" t="n">
-        <v>6685585</v>
+        <v>6685692</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -1617,7 +1522,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1627,7 +1532,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1654,62 +1559,60 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121791487</v>
+        <v>121795522</v>
       </c>
       <c r="B10" t="n">
-        <v>98159</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>661747</v>
+        <v>661736</v>
       </c>
       <c r="R10" t="n">
-        <v>6685756</v>
+        <v>6685773</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1736,9 +1639,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,31 +1666,26 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121795526</v>
+        <v>121795524</v>
       </c>
       <c r="B11" t="n">
-        <v>57390</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1807,7 +1715,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1817,10 +1725,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>661776</v>
+        <v>661817</v>
       </c>
       <c r="R11" t="n">
-        <v>6685559</v>
+        <v>6685662</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1852,7 +1760,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1862,7 +1770,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1889,62 +1797,60 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121791510</v>
+        <v>121795526</v>
       </c>
       <c r="B12" t="n">
-        <v>98159</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>661731</v>
+        <v>661776</v>
       </c>
       <c r="R12" t="n">
-        <v>6685770</v>
+        <v>6685559</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1971,9 +1877,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,31 +1904,26 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121795518</v>
+        <v>121795528</v>
       </c>
       <c r="B13" t="n">
-        <v>57390</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2042,20 +1953,20 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Storbya hjortronmosse, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>661615</v>
+        <v>661695</v>
       </c>
       <c r="R13" t="n">
-        <v>6685669</v>
+        <v>6685522</v>
       </c>
       <c r="S13" t="n">
         <v>4</v>
@@ -2087,7 +1998,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,7 +2008,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2124,19 +2035,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121795524</v>
+        <v>121795530</v>
       </c>
       <c r="B14" t="n">
-        <v>57390</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2172,14 +2078,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Storbya hjortronmosse, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>661817</v>
+        <v>661649</v>
       </c>
       <c r="R14" t="n">
-        <v>6685662</v>
+        <v>6685585</v>
       </c>
       <c r="S14" t="n">
         <v>4</v>
@@ -2211,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2221,7 +2127,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,62 +2154,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121795520</v>
+        <v>121795512</v>
       </c>
       <c r="B15" t="n">
-        <v>57390</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Andersön, Upl</t>
+          <t>Storbya hjortronmosse, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>661629</v>
+        <v>661645</v>
       </c>
       <c r="R15" t="n">
-        <v>6685692</v>
+        <v>6685564</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2335,7 +2233,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2345,7 +2243,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2372,53 +2270,57 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121791202</v>
+        <v>121795514</v>
       </c>
       <c r="B16" t="n">
-        <v>95706</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>105930</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Andersön, Andersön, Upl</t>
+          <t>Storbya hjortronmosse, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>661692</v>
+        <v>661711</v>
       </c>
       <c r="R16" t="n">
-        <v>6685628</v>
+        <v>6685529</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2445,9 +2347,19 @@
           <t>2024-12-30</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2462,77 +2374,69 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Annika Rastén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121795532</v>
+        <v>121791487</v>
       </c>
       <c r="B17" t="n">
-        <v>57634</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gyltaholmarna, Upl</t>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>661892</v>
+        <v>661747</v>
       </c>
       <c r="R17" t="n">
-        <v>6685589</v>
+        <v>6685756</v>
       </c>
       <c r="S17" t="n">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2559,19 +2463,9 @@
           <t>2024-12-30</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-12-30</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:32</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,15 +2480,465 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>121791510</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gyltaholmarna, Gyltaholmarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>661731</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6685770</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>121795556</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Andersön, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>661611</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6685709</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY17" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121795558</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gyltaholmarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>661739</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6685755</v>
+      </c>
+      <c r="S20" t="n">
+        <v>4</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:43</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-12-30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>4956367</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sjudars, 1,0 km V-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>661708</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6685644</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2011-10-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2011-10-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55518-2024 artfynd.xlsx
+++ b/artfynd/A 55518-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121791202</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121795546</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121795537</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121795539</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1161035</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1771771</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121795518</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121795520</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1675,6 +1720,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121795522</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1794,6 +1844,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121795524</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1913,6 +1968,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121795526</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2032,6 +2092,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121795528</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2151,6 +2216,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121795530</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2267,6 +2337,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121795512</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2383,6 +2458,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121795514</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2489,6 +2569,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121791487</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2595,6 +2680,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121791510</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2714,6 +2804,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121795556</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2833,6 +2928,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121795558</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2939,8 +3039,35 @@
           <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4956367</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>